--- a/01-Raw-Data/NB-Yearly-Crossings-2013-2024.xlsx
+++ b/01-Raw-Data/NB-Yearly-Crossings-2013-2024.xlsx
@@ -8,17 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myunt.sharepoint.com/sites/TxDOT20252026UNTInteragencyContract/Shared Documents/General/Task 1 - Bridges and Border Crossings Guide/Task 1.3 - Texas-Mexico Border Database/CBP-Border-Corssings/01-Raw-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="11_7227FE96A489B014265460A215AC4E675B1376FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0689052-5725-46C0-BCB4-50BB88A648CB}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="11_7227FE96A489B014265460A215AC4E675B1376FD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D1686994-B18D-4CBA-A24C-6C996B62C527}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="615" windowWidth="42225" windowHeight="23385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="15480" yWindow="0" windowWidth="42225" windowHeight="23280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2013-2024 CBP" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="2013-2024 CBP" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2013-2024 CBP'!$A$1:$G$1981</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'2013-2024 CBP'!$A$1:$G$1981</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
+  <pivotCaches>
+    <pivotCache cacheId="3" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11887" uniqueCount="2050">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11895" uniqueCount="2053">
   <si>
     <t>ID</t>
   </si>
@@ -6189,6 +6193,15 @@
   </si>
   <si>
     <t>Pedestrians/ Bicyclists</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>(blank)</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
   </si>
 </sst>
 </file>
@@ -6226,9 +6239,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6248,6 +6265,6036 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Adithya Ajith" refreshedDate="46131.964715972223" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="1981" xr:uid="{DA4CE3FF-1FD0-49DF-BC11-09BBF31F8D03}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="F1:F1048576" sheet="2013-2024 CBP"/>
+  </cacheSource>
+  <cacheFields count="1">
+    <cacheField name="Modes" numFmtId="0">
+      <sharedItems containsBlank="1" count="6">
+        <s v="Commercial Trucks"/>
+        <s v="Buses"/>
+        <s v="Pedestrians/ Bicyclists"/>
+        <s v="Passenger Vehicles"/>
+        <s v="Railcars"/>
+        <m/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="1981">
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+  </r>
+  <r>
+    <x v="2"/>
+  </r>
+  <r>
+    <x v="3"/>
+  </r>
+  <r>
+    <x v="4"/>
+  </r>
+  <r>
+    <x v="5"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBA5BFCE-E88A-4EBE-91C0-5ED567F76A57}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:A10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="1">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6566,6 +12613,59 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471EF493-AFB7-41E9-AE71-3BC65322B28E}">
+  <dimension ref="A3:A10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G1981"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
